--- a/resources/templates/standard/L3100-03.xlsx
+++ b/resources/templates/standard/L3100-03.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">결
 재</t>
@@ -563,7 +566,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -580,17 +585,17 @@
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S1" s="4"/>
       <c r="T1" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="36.75" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
@@ -641,24 +646,24 @@
     </row>
     <row r="4" ht="21.95" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
@@ -672,28 +677,28 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -707,7 +712,7 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U5" s="5"/>
     </row>
